--- a/exports/trend_1d/PETRONET_full_report.xlsx
+++ b/exports/trend_1d/PETRONET_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:U76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>8.18</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42033</v>
+        <v>42034</v>
       </c>
       <c r="H2" t="n">
-        <v>86.45</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>85.16499999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>-6.79</v>
+        <v>-10.62</v>
       </c>
       <c r="L2" t="n">
-        <v>7.12</v>
+        <v>12.18</v>
       </c>
       <c r="M2" t="n">
         <v>0.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>4.11</v>
       </c>
       <c r="O2" t="n">
         <v>-0.96</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.28</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42143</v>
+        <v>42144</v>
       </c>
       <c r="H3" t="n">
-        <v>85.15000000000001</v>
+        <v>85.95</v>
       </c>
       <c r="I3" t="n">
         <v>85.33518352880102</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.71</v>
+        <v>-3.68</v>
       </c>
       <c r="L3" t="n">
         <v>9.35</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.3</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42235</v>
+        <v>42236</v>
       </c>
       <c r="H4" t="n">
-        <v>85.45</v>
+        <v>82.55</v>
       </c>
       <c r="I4" t="n">
         <v>84.15463533118319</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.58</v>
+        <v>-3.96</v>
       </c>
       <c r="L4" t="n">
         <v>7.8</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>11.97</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42293</v>
+        <v>42296</v>
       </c>
       <c r="H5" t="n">
-        <v>87.40000000000001</v>
+        <v>88.25</v>
       </c>
       <c r="I5" t="n">
         <v>87.52497423135345</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.88</v>
+        <v>-6.9</v>
       </c>
       <c r="L5" t="n">
-        <v>6.9</v>
+        <v>7.87</v>
       </c>
       <c r="M5" t="n">
         <v>2.37</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.93</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42388.38541666666</v>
+        <v>42389.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>114.4</v>
+        <v>111.6</v>
       </c>
       <c r="I6" t="n">
         <v>112.152090720041</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>92.38541666666667</v>
+        <v>93.38541666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>29.63</v>
+        <v>26.46</v>
       </c>
       <c r="L6" t="n">
         <v>5.44</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.19</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42471.38541666666</v>
+        <v>42472.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>112.7</v>
+        <v>119.2</v>
       </c>
       <c r="I7" t="n">
         <v>118.696253752364</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.99</v>
+        <v>-6.81</v>
       </c>
       <c r="L7" t="n">
         <v>9.99</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.71</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42510.38541666666</v>
+        <v>42513.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>121.8</v>
+        <v>119.6</v>
       </c>
       <c r="I8" t="n">
         <v>120.3214285925696</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K8" t="n">
-        <v>2.18</v>
+        <v>0.34</v>
       </c>
       <c r="L8" t="n">
         <v>5.66</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42517.38541666666</v>
+        <v>42520.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>125.9</v>
+        <v>128.35</v>
       </c>
       <c r="I9" t="n">
         <v>127.3472455006026</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.27</v>
+        <v>-7.32</v>
       </c>
       <c r="L9" t="n">
-        <v>6.65</v>
+        <v>7.82</v>
       </c>
       <c r="M9" t="n">
         <v>0.8100000000000001</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.02</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42622.38541666666</v>
+        <v>42625.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>161.15</v>
+        <v>152.05</v>
       </c>
       <c r="I10" t="n">
         <v>152.9691190216242</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K10" t="n">
-        <v>25.56</v>
+        <v>18.47</v>
       </c>
       <c r="L10" t="n">
         <v>4.67</v>
@@ -1011,7 +1130,7 @@
         <v>1.17</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>5.65</v>
       </c>
       <c r="O10" t="n">
         <v>1.95</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>12.36</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42646.38541666666</v>
+        <v>42647.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>162.7</v>
+        <v>169.3</v>
       </c>
       <c r="I11" t="n">
         <v>168.1607920353838</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>-7</v>
+        <v>-11.34</v>
       </c>
       <c r="L11" t="n">
-        <v>7.86</v>
+        <v>12.07</v>
       </c>
       <c r="M11" t="n">
         <v>0.91</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>4.06</v>
       </c>
       <c r="O11" t="n">
         <v>-5.65</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.98</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42676.38541666666</v>
+        <v>42677.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>169.15</v>
+        <v>164.15</v>
       </c>
       <c r="I12" t="n">
         <v>168.7068250622634</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.09</v>
+        <v>-3.04</v>
       </c>
       <c r="L12" t="n">
         <v>4.37</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>12.46</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42760.38541666666</v>
+        <v>42762.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>172.7</v>
+        <v>181.1</v>
       </c>
       <c r="I13" t="n">
         <v>178.1953536240583</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.21</v>
+        <v>-10.33</v>
       </c>
       <c r="L13" t="n">
         <v>11.33</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.43</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42933.38541666666</v>
+        <v>42934.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>192.8</v>
+        <v>191</v>
       </c>
       <c r="I14" t="n">
         <v>191.0991675800093</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K14" t="n">
-        <v>6.46</v>
+        <v>5.47</v>
       </c>
       <c r="L14" t="n">
         <v>5.77</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>7.65</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42958.38541666666</v>
+        <v>42961.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>194.45</v>
+        <v>200.4</v>
       </c>
       <c r="I15" t="n">
         <v>199.2247767663623</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.81</v>
+        <v>-4.92</v>
       </c>
       <c r="L15" t="n">
-        <v>4.92</v>
+        <v>5.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9</v>
+        <v>1.72</v>
       </c>
       <c r="N15" t="n">
         <v>3.8</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>11.72</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43070.38541666666</v>
+        <v>43073.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>224.75</v>
+        <v>223.5</v>
       </c>
       <c r="I16" t="n">
         <v>224.7400242566796</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K16" t="n">
-        <v>12.15</v>
+        <v>11.53</v>
       </c>
       <c r="L16" t="n">
         <v>2.59</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43129.38541666666</v>
+        <v>43130.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>230.9</v>
+        <v>237.75</v>
       </c>
       <c r="I17" t="n">
         <v>234.484627413034</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.31</v>
+        <v>-6.38</v>
       </c>
       <c r="L17" t="n">
         <v>7.2</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>10.11</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43167.38541666666</v>
+        <v>43168.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>216.95</v>
+        <v>212.65</v>
       </c>
       <c r="I18" t="n">
         <v>214.3180687456909</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K18" t="n">
-        <v>-8.75</v>
+        <v>-10.56</v>
       </c>
       <c r="L18" t="n">
-        <v>10.12</v>
+        <v>11.42</v>
       </c>
       <c r="M18" t="n">
         <v>4.84</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.42</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43306.38541666666</v>
+        <v>43307.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>203.8</v>
+        <v>213.15</v>
       </c>
       <c r="I19" t="n">
         <v>208.2337308788907</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K19" t="n">
-        <v>4.16</v>
+        <v>-0.24</v>
       </c>
       <c r="L19" t="n">
         <v>6.35</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>10.38</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43367.38541666666</v>
+        <v>43368.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>209.3</v>
+        <v>206.05</v>
       </c>
       <c r="I20" t="n">
         <v>207.5242156170421</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.81</v>
+        <v>-3.33</v>
       </c>
       <c r="L20" t="n">
         <v>6.59</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>11.77</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43448</v>
+        <v>43451</v>
       </c>
       <c r="H21" t="n">
-        <v>200.3</v>
+        <v>207.45</v>
       </c>
       <c r="I21" t="n">
         <v>205.7669535550017</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>79.61458333333333</v>
+        <v>82.61458333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>2.79</v>
+        <v>-0.68</v>
       </c>
       <c r="L21" t="n">
         <v>4</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>9.81</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43497</v>
+        <v>43500</v>
       </c>
       <c r="H22" t="n">
-        <v>203.8</v>
+        <v>193.55</v>
       </c>
       <c r="I22" t="n">
         <v>196.7060523336889</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.76</v>
+        <v>-6.7</v>
       </c>
       <c r="L22" t="n">
-        <v>6.34</v>
+        <v>7.57</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>3.54</v>
+        <v>5.03</v>
       </c>
       <c r="O22" t="n">
         <v>3.57</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>12.44</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43531</v>
+        <v>43532</v>
       </c>
       <c r="H23" t="n">
-        <v>211.1</v>
+        <v>215.6</v>
       </c>
       <c r="I23" t="n">
         <v>213.6083515369695</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K23" t="n">
-        <v>-9.07</v>
+        <v>-11.39</v>
       </c>
       <c r="L23" t="n">
-        <v>10.95</v>
+        <v>11.88</v>
       </c>
       <c r="M23" t="n">
         <v>1.18</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>8.31</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43600</v>
+        <v>43601</v>
       </c>
       <c r="H24" t="n">
-        <v>215.1</v>
+        <v>206.65</v>
       </c>
       <c r="I24" t="n">
         <v>211.1615707443628</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.23</v>
+        <v>-4.15</v>
       </c>
       <c r="L24" t="n">
-        <v>2.27</v>
+        <v>6.26</v>
       </c>
       <c r="M24" t="n">
-        <v>1.12</v>
+        <v>2.67</v>
       </c>
       <c r="N24" t="n">
-        <v>2.42</v>
+        <v>3.93</v>
       </c>
       <c r="O24" t="n">
         <v>2.13</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>9.41</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43615</v>
+        <v>43616</v>
       </c>
       <c r="H25" t="n">
-        <v>223.55</v>
+        <v>227.75</v>
       </c>
       <c r="I25" t="n">
         <v>226.1033467621798</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>-8.18</v>
+        <v>-10.21</v>
       </c>
       <c r="L25" t="n">
         <v>11.86</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43670</v>
+        <v>43671</v>
       </c>
       <c r="H26" t="n">
-        <v>216.35</v>
+        <v>214.1</v>
       </c>
       <c r="I26" t="n">
         <v>215.9693397642311</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.01</v>
+        <v>-5.99</v>
       </c>
       <c r="L26" t="n">
         <v>8.210000000000001</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43703</v>
+        <v>43704</v>
       </c>
       <c r="H27" t="n">
-        <v>226.75</v>
+        <v>238.25</v>
       </c>
       <c r="I27" t="n">
         <v>232.3751951776898</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.91</v>
+        <v>-11.28</v>
       </c>
       <c r="L27" t="n">
-        <v>6.33</v>
+        <v>11.75</v>
       </c>
       <c r="M27" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>5.07</v>
       </c>
       <c r="O27" t="n">
         <v>-1.04</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.71</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43790</v>
+        <v>43791</v>
       </c>
       <c r="H28" t="n">
-        <v>251.3</v>
+        <v>244.05</v>
       </c>
       <c r="I28" t="n">
         <v>245.3918326031003</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K28" t="n">
-        <v>5.48</v>
+        <v>2.43</v>
       </c>
       <c r="L28" t="n">
         <v>4.76</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43949</v>
+        <v>43950</v>
       </c>
       <c r="H29" t="n">
-        <v>206.85</v>
+        <v>217.05</v>
       </c>
       <c r="I29" t="n">
         <v>213.1374600629235</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K29" t="n">
-        <v>15.24</v>
+        <v>11.06</v>
       </c>
       <c r="L29" t="n">
         <v>7.01</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>6</v>
+      </c>
+      <c r="U29" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>17.67</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44035</v>
+        <v>44036</v>
       </c>
       <c r="H30" t="n">
-        <v>232.1</v>
+        <v>222.35</v>
       </c>
       <c r="I30" t="n">
         <v>229.7675549512063</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K30" t="n">
-        <v>6.93</v>
+        <v>2.44</v>
       </c>
       <c r="L30" t="n">
         <v>7.62</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>13.07</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44055</v>
+        <v>44056</v>
       </c>
       <c r="H31" t="n">
-        <v>237.9</v>
+        <v>244.45</v>
       </c>
       <c r="I31" t="n">
         <v>242.1277909913774</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.99</v>
+        <v>-9.94</v>
       </c>
       <c r="L31" t="n">
-        <v>7.51</v>
+        <v>10.28</v>
       </c>
       <c r="M31" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="N31" t="n">
         <v>4.57</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>10.71</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44077</v>
+        <v>44078</v>
       </c>
       <c r="H32" t="n">
-        <v>220.45</v>
+        <v>216.7</v>
       </c>
       <c r="I32" t="n">
         <v>218.2808530948407</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K32" t="n">
-        <v>-9.82</v>
+        <v>-11.35</v>
       </c>
       <c r="L32" t="n">
-        <v>11.09</v>
+        <v>11.72</v>
       </c>
       <c r="M32" t="n">
-        <v>0.53</v>
+        <v>1.32</v>
       </c>
       <c r="N32" t="n">
         <v>3.59</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.05</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44125</v>
+        <v>44126</v>
       </c>
       <c r="H33" t="n">
-        <v>207.1</v>
+        <v>217.15</v>
       </c>
       <c r="I33" t="n">
         <v>212.642007052523</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K33" t="n">
-        <v>4.43</v>
+        <v>-0.21</v>
       </c>
       <c r="L33" t="n">
         <v>3.3</v>
@@ -2322,7 +2717,7 @@
         <v>1.39</v>
       </c>
       <c r="N33" t="n">
-        <v>4.07</v>
+        <v>4.85</v>
       </c>
       <c r="O33" t="n">
         <v>-1.7</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.7</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c r="H34" t="n">
-        <v>239.4</v>
+        <v>224.25</v>
       </c>
       <c r="I34" t="n">
         <v>228.7527657173568</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K34" t="n">
-        <v>10.25</v>
+        <v>3.27</v>
       </c>
       <c r="L34" t="n">
         <v>5.92</v>
@@ -2379,7 +2786,7 @@
         <v>1.71</v>
       </c>
       <c r="N34" t="n">
-        <v>5.43</v>
+        <v>6.33</v>
       </c>
       <c r="O34" t="n">
         <v>4.85</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>14.73</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44308</v>
+        <v>44309</v>
       </c>
       <c r="H35" t="n">
-        <v>211.85</v>
+        <v>216.75</v>
       </c>
       <c r="I35" t="n">
         <v>216.2094490691837</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K35" t="n">
-        <v>5.53</v>
+        <v>3.34</v>
       </c>
       <c r="L35" t="n">
         <v>7.25</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>10.23</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44355</v>
+        <v>44356</v>
       </c>
       <c r="H36" t="n">
-        <v>228.7</v>
+        <v>210.45</v>
       </c>
       <c r="I36" t="n">
         <v>215.5698324222653</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K36" t="n">
-        <v>5.51</v>
+        <v>-2.91</v>
       </c>
       <c r="L36" t="n">
         <v>3.46</v>
       </c>
       <c r="M36" t="n">
-        <v>1.65</v>
+        <v>2.86</v>
       </c>
       <c r="N36" t="n">
-        <v>2.83</v>
+        <v>7.98</v>
       </c>
       <c r="O36" t="n">
         <v>2.31</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>12.56</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44426</v>
+        <v>44428</v>
       </c>
       <c r="H37" t="n">
-        <v>206.15</v>
+        <v>209.15</v>
       </c>
       <c r="I37" t="n">
         <v>207.593215120819</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K37" t="n">
-        <v>2.04</v>
+        <v>0.62</v>
       </c>
       <c r="L37" t="n">
         <v>7.94</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.47</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44517</v>
+        <v>44518</v>
       </c>
       <c r="H38" t="n">
-        <v>210.2</v>
+        <v>207.7</v>
       </c>
       <c r="I38" t="n">
         <v>209.2715481839672</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L38" t="n">
         <v>2.96</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.86</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44571</v>
+        <v>44572</v>
       </c>
       <c r="H39" t="n">
-        <v>205.85</v>
+        <v>208.55</v>
       </c>
       <c r="I39" t="n">
         <v>206.7503081306457</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K39" t="n">
-        <v>0.89</v>
+        <v>-0.41</v>
       </c>
       <c r="L39" t="n">
         <v>2.21</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.08</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H40" t="n">
-        <v>199.2</v>
+        <v>196.2</v>
       </c>
       <c r="I40" t="n">
         <v>197.7052600077994</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.48</v>
+        <v>-5.92</v>
       </c>
       <c r="L40" t="n">
-        <v>4.72</v>
+        <v>6.47</v>
       </c>
       <c r="M40" t="n">
         <v>0.53</v>
       </c>
       <c r="N40" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="O40" t="n">
         <v>1.31</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>6.57</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44602</v>
+        <v>44603</v>
       </c>
       <c r="H41" t="n">
-        <v>202.35</v>
+        <v>206.1</v>
       </c>
       <c r="I41" t="n">
         <v>205.5550214745755</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.13</v>
+        <v>-5.05</v>
       </c>
       <c r="L41" t="n">
-        <v>4.77</v>
+        <v>5.4</v>
       </c>
       <c r="M41" t="n">
         <v>2.29</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.32</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44614</v>
+        <v>44615</v>
       </c>
       <c r="H42" t="n">
-        <v>191.05</v>
+        <v>189.2</v>
       </c>
       <c r="I42" t="n">
         <v>191.0043000686665</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>-7.3</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L42" t="n">
         <v>8.880000000000001</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>8.18</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44617</v>
+        <v>44620</v>
       </c>
       <c r="H43" t="n">
-        <v>188.55</v>
+        <v>198.45</v>
       </c>
       <c r="I43" t="n">
         <v>197.6752460014695</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>0.34</v>
+        <v>-4.89</v>
       </c>
       <c r="L43" t="n">
-        <v>2.22</v>
+        <v>5.55</v>
       </c>
       <c r="M43" t="n">
         <v>3.66</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>13.3</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44637</v>
+        <v>44641</v>
       </c>
       <c r="H44" t="n">
-        <v>190.35</v>
+        <v>179.65</v>
       </c>
       <c r="I44" t="n">
         <v>183.6992374482598</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.08</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>7.11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>0.91</v>
+        <v>1.68</v>
       </c>
       <c r="N44" t="n">
-        <v>3.68</v>
+        <v>5.62</v>
       </c>
       <c r="O44" t="n">
         <v>5.25</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>12.48</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44671</v>
+        <v>44672</v>
       </c>
       <c r="H45" t="n">
-        <v>190.55</v>
+        <v>194.25</v>
       </c>
       <c r="I45" t="n">
         <v>193.1602968501102</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.07</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>6.4</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M45" t="n">
         <v>0.8100000000000001</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>7.07</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44728</v>
+        <v>44729</v>
       </c>
       <c r="H46" t="n">
-        <v>196.95</v>
+        <v>187.4</v>
       </c>
       <c r="I46" t="n">
         <v>193.164489495642</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K46" t="n">
-        <v>1.39</v>
+        <v>-3.53</v>
       </c>
       <c r="L46" t="n">
         <v>5.05</v>
       </c>
       <c r="M46" t="n">
-        <v>4.7</v>
+        <v>4.98</v>
       </c>
       <c r="N46" t="n">
-        <v>2.51</v>
+        <v>4.85</v>
       </c>
       <c r="O46" t="n">
         <v>1.94</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>11.85</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44742</v>
+        <v>44743</v>
       </c>
       <c r="H47" t="n">
-        <v>200.3</v>
+        <v>204.15</v>
       </c>
       <c r="I47" t="n">
         <v>203.1253559802366</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.88</v>
+        <v>-8.94</v>
       </c>
       <c r="L47" t="n">
-        <v>7.92</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="M47" t="n">
         <v>0.91</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44778</v>
+        <v>44781</v>
       </c>
       <c r="H48" t="n">
-        <v>199</v>
+        <v>194.2</v>
       </c>
       <c r="I48" t="n">
         <v>195.2316825987834</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.52</v>
+        <v>-4.87</v>
       </c>
       <c r="L48" t="n">
-        <v>4.24</v>
+        <v>5.98</v>
       </c>
       <c r="M48" t="n">
         <v>2.16</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.26</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44869</v>
+        <v>44872</v>
       </c>
       <c r="H49" t="n">
-        <v>194.25</v>
+        <v>195.9</v>
       </c>
       <c r="I49" t="n">
         <v>195.3068643341956</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.03</v>
+        <v>-0.88</v>
       </c>
       <c r="L49" t="n">
         <v>6.1</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.83</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44957</v>
+        <v>44958</v>
       </c>
       <c r="H50" t="n">
-        <v>200.25</v>
+        <v>199.5</v>
       </c>
       <c r="I50" t="n">
         <v>199.7688346075127</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K50" t="n">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="L50" t="n">
         <v>3.5</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>7.22</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44991</v>
+        <v>44993</v>
       </c>
       <c r="H51" t="n">
-        <v>206.9</v>
+        <v>212.25</v>
       </c>
       <c r="I51" t="n">
         <v>207.6434275431139</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.71</v>
+        <v>-6.39</v>
       </c>
       <c r="L51" t="n">
-        <v>4.54</v>
+        <v>6.69</v>
       </c>
       <c r="M51" t="n">
         <v>0.73</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.23</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45051</v>
+        <v>45054</v>
       </c>
       <c r="H52" t="n">
-        <v>208.55</v>
+        <v>206.4</v>
       </c>
       <c r="I52" t="n">
         <v>207.6679427648</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.74</v>
+        <v>-2.76</v>
       </c>
       <c r="L52" t="n">
         <v>4.43</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.7</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45113</v>
+        <v>45114</v>
       </c>
       <c r="H53" t="n">
-        <v>210.55</v>
+        <v>211.8</v>
       </c>
       <c r="I53" t="n">
         <v>211.5124112843304</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.01</v>
+        <v>-2.62</v>
       </c>
       <c r="L53" t="n">
         <v>4.05</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>4.49</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45155</v>
+        <v>45156</v>
       </c>
       <c r="H54" t="n">
-        <v>206.25</v>
+        <v>202.15</v>
       </c>
       <c r="I54" t="n">
         <v>205.4776724066516</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.62</v>
+        <v>-4.56</v>
       </c>
       <c r="L54" t="n">
-        <v>3.59</v>
+        <v>4.89</v>
       </c>
       <c r="M54" t="n">
-        <v>0.75</v>
+        <v>1.62</v>
       </c>
       <c r="N54" t="n">
         <v>3.51</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>6.3</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45173</v>
+        <v>45174</v>
       </c>
       <c r="H55" t="n">
-        <v>201.9</v>
+        <v>211.25</v>
       </c>
       <c r="I55" t="n">
         <v>208.9817800827114</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K55" t="n">
-        <v>0.12</v>
+        <v>-4.5</v>
       </c>
       <c r="L55" t="n">
-        <v>1.58</v>
+        <v>4.77</v>
       </c>
       <c r="M55" t="n">
         <v>0.33</v>
       </c>
       <c r="N55" t="n">
-        <v>1.97</v>
+        <v>4.63</v>
       </c>
       <c r="O55" t="n">
         <v>-1.99</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.41</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="H56" t="n">
-        <v>216.5</v>
+        <v>214.1</v>
       </c>
       <c r="I56" t="n">
         <v>214.4041943074574</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K56" t="n">
-        <v>2.49</v>
+        <v>1.35</v>
       </c>
       <c r="L56" t="n">
         <v>4.24</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.43</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="H57" t="n">
-        <v>195.95</v>
+        <v>196.95</v>
       </c>
       <c r="I57" t="n">
         <v>196.9182053065869</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K57" t="n">
-        <v>8.48</v>
+        <v>8.01</v>
       </c>
       <c r="L57" t="n">
         <v>2.17</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.89</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H58" t="n">
-        <v>263.3</v>
+        <v>251.9</v>
       </c>
       <c r="I58" t="n">
         <v>252.1892312118474</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K58" t="n">
-        <v>33.69</v>
+        <v>27.9</v>
       </c>
       <c r="L58" t="n">
         <v>1.17</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>13.18</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="H59" t="n">
-        <v>260.6</v>
+        <v>270.2</v>
       </c>
       <c r="I59" t="n">
         <v>269.9300966860878</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.45</v>
+        <v>-7.26</v>
       </c>
       <c r="L59" t="n">
-        <v>5.52</v>
+        <v>9.09</v>
       </c>
       <c r="M59" t="n">
         <v>0.82</v>
       </c>
       <c r="N59" t="n">
-        <v>2.8</v>
+        <v>3.68</v>
       </c>
       <c r="O59" t="n">
         <v>-4.33</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>10.13</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H60" t="n">
-        <v>302.55</v>
+        <v>265.45</v>
       </c>
       <c r="I60" t="n">
         <v>272.9571907823458</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K60" t="n">
-        <v>11.97</v>
+        <v>-1.76</v>
       </c>
       <c r="L60" t="n">
-        <v>3.63</v>
+        <v>10.42</v>
       </c>
       <c r="M60" t="n">
         <v>1.7</v>
       </c>
       <c r="N60" t="n">
-        <v>3.73</v>
+        <v>12.26</v>
       </c>
       <c r="O60" t="n">
         <v>3.68</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>18.47</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45470</v>
+        <v>45471</v>
       </c>
       <c r="H61" t="n">
-        <v>305.7</v>
+        <v>315.5</v>
       </c>
       <c r="I61" t="n">
         <v>310.5637823831079</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K61" t="n">
-        <v>-15.16</v>
+        <v>-18.85</v>
       </c>
       <c r="L61" t="n">
         <v>20.21</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>10.65</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45541</v>
+        <v>45544</v>
       </c>
       <c r="H62" t="n">
-        <v>338.15</v>
+        <v>327.65</v>
       </c>
       <c r="I62" t="n">
         <v>336.9590420508531</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K62" t="n">
-        <v>7.18</v>
+        <v>3.85</v>
       </c>
       <c r="L62" t="n">
         <v>2.76</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H63" t="n">
-        <v>328.7</v>
+        <v>348.15</v>
       </c>
       <c r="I63" t="n">
         <v>334.1985903392181</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.32</v>
+        <v>-6.26</v>
       </c>
       <c r="L63" t="n">
-        <v>2.75</v>
+        <v>6.97</v>
       </c>
       <c r="M63" t="n">
         <v>0.88</v>
       </c>
       <c r="N63" t="n">
-        <v>2.18</v>
+        <v>5.92</v>
       </c>
       <c r="O63" t="n">
         <v>-3.11</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>11.25</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45590</v>
+        <v>45593</v>
       </c>
       <c r="H64" t="n">
-        <v>322.45</v>
+        <v>316.6</v>
       </c>
       <c r="I64" t="n">
         <v>316.9819422245444</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.38</v>
+        <v>-9.06</v>
       </c>
       <c r="L64" t="n">
-        <v>8.56</v>
+        <v>11</v>
       </c>
       <c r="M64" t="n">
         <v>1.19</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,25 +4904,25 @@
         <v>9.43</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H65" t="n">
-        <v>324.75</v>
+        <v>330.05</v>
       </c>
       <c r="I65" t="n">
         <v>328.413745928503</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.57</v>
+        <v>-4.25</v>
       </c>
       <c r="L65" t="n">
-        <v>5.57</v>
+        <v>5.61</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="N65" t="n">
         <v>3.15</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>7.37</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H66" t="n">
-        <v>318.7</v>
+        <v>312.3</v>
       </c>
       <c r="I66" t="n">
         <v>315.431760604952</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.44</v>
+        <v>-5.38</v>
       </c>
       <c r="L66" t="n">
         <v>6.14</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>9.66</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H67" t="n">
-        <v>296.3</v>
+        <v>305.75</v>
       </c>
       <c r="I67" t="n">
         <v>296.551832321391</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K67" t="n">
-        <v>5.12</v>
+        <v>2.1</v>
       </c>
       <c r="L67" t="n">
         <v>3.76</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>11.11</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H68" t="n">
-        <v>289.7</v>
+        <v>283.8</v>
       </c>
       <c r="I68" t="n">
         <v>288.8511147928559</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K68" t="n">
-        <v>-5.25</v>
+        <v>-7.18</v>
       </c>
       <c r="L68" t="n">
         <v>7.51</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="H69" t="n">
-        <v>273.25</v>
+        <v>280.35</v>
       </c>
       <c r="I69" t="n">
         <v>274.1413162547558</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K69" t="n">
-        <v>3.72</v>
+        <v>1.22</v>
       </c>
       <c r="L69" t="n">
         <v>7.66</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>6.77</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H70" t="n">
-        <v>280.05</v>
+        <v>273.75</v>
       </c>
       <c r="I70" t="n">
         <v>277.4409547302351</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.11</v>
+        <v>-2.35</v>
       </c>
       <c r="L70" t="n">
         <v>6.01</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>9.01</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H71" t="n">
-        <v>290.2</v>
+        <v>297.4</v>
       </c>
       <c r="I71" t="n">
         <v>296.4033060618855</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.01</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>8.77</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="M71" t="n">
         <v>2.16</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>10.17</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H72" t="n">
-        <v>308.65</v>
+        <v>280</v>
       </c>
       <c r="I72" t="n">
         <v>298.4496774844721</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K72" t="n">
-        <v>3.78</v>
+        <v>-5.85</v>
       </c>
       <c r="L72" t="n">
-        <v>3.82</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M72" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="N72" t="n">
-        <v>4.56</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="O72" t="n">
         <v>2.48</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>13.92</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="H73" t="n">
-        <v>273.45</v>
+        <v>279.9</v>
       </c>
       <c r="I73" t="n">
         <v>279.7978071240555</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K73" t="n">
-        <v>2.34</v>
+        <v>0.04</v>
       </c>
       <c r="L73" t="n">
         <v>7.84</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="H74" t="n">
-        <v>279.65</v>
+        <v>269.45</v>
       </c>
       <c r="I74" t="n">
         <v>269.8368435136673</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.09</v>
+        <v>-3.73</v>
       </c>
       <c r="L74" t="n">
         <v>7.04</v>
@@ -4659,7 +5546,7 @@
         <v>1.39</v>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="O74" t="n">
         <v>2.36</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -4695,25 +5594,25 @@
         <v>8.19</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H75" t="n">
-        <v>288.15</v>
+        <v>291.4</v>
       </c>
       <c r="I75" t="n">
         <v>290.7227293201796</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K75" t="n">
-        <v>-6.94</v>
+        <v>-8.15</v>
       </c>
       <c r="L75" t="n">
-        <v>8.18</v>
+        <v>9.02</v>
       </c>
       <c r="M75" t="n">
-        <v>0.15</v>
+        <v>0.64</v>
       </c>
       <c r="N75" t="n">
         <v>1.95</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4776,6 +5687,14 @@
       <c r="Q76" t="n">
         <v>47</v>
       </c>
+      <c r="R76" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9734,7 +10653,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.6</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="6">
@@ -9744,7 +10663,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -9754,7 +10673,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8">
@@ -9764,7 +10683,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -9774,7 +10693,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -9784,7 +10703,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100.8</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="11">
@@ -9794,7 +10713,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -9804,7 +10723,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -9814,7 +10733,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.4</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="14">
@@ -9824,7 +10743,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.41</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="15">
@@ -9834,7 +10753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.53</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="16">
@@ -9844,7 +10763,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.71</v>
+        <v>-4.61</v>
       </c>
     </row>
     <row r="17">
@@ -9854,7 +10773,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>33.69</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="18">
@@ -9864,7 +10783,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>40.5</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="19">
@@ -9874,7 +10793,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.14</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="20">
@@ -9884,7 +10803,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.06</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="21">
@@ -9904,7 +10823,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
@@ -9914,7 +10833,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -9924,7 +10843,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="25">
@@ -9944,7 +10863,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.01</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="27">
@@ -9954,7 +10873,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.24</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="28">
@@ -9964,7 +10883,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
